--- a/public/EmployeeTemplate.xlsx
+++ b/public/EmployeeTemplate.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10611"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/julia4/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MM-HO HP New\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CA13BC5-6FCD-D94E-A340-369538CB5230}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C65C01A-BA53-47D6-B1F9-95BCC3243555}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="20740" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Import Employee Template" sheetId="1" r:id="rId1"/>
@@ -169,7 +169,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;TRUE&quot;;&quot;TRUE&quot;;&quot;FALSE&quot;"/>
   </numFmts>
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -311,13 +311,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="12"/>
@@ -681,19 +674,18 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="42"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1082,38 +1074,38 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AA11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="18" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.83203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.42578125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="20.5" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="20" style="4" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="18.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="18.1640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.1640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="15.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="26" style="4" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="20" style="3" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="18.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="26" style="3" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="26" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="27.83203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="27.85546875" style="7" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="32" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="22.33203125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="5.5" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="22.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="10.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1156,34 +1148,34 @@
       <c r="N1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="O1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="P1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="Q1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="R1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="4" t="s">
+      <c r="S1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="4" t="s">
+      <c r="T1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="4" t="s">
+      <c r="U1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="7" t="s">
+      <c r="V1" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="4" t="s">
+      <c r="W1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="X1" t="s">
+      <c r="X1" s="3" t="s">
         <v>23</v>
       </c>
       <c r="Y1" t="s">
@@ -1196,14 +1188,14 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:27" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>39</v>
       </c>
       <c r="B2" t="s">
         <v>40</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="7" t="s">
         <v>36</v>
       </c>
       <c r="D2" s="2" t="s">
@@ -1239,37 +1231,37 @@
       <c r="N2">
         <v>20</v>
       </c>
-      <c r="O2" s="5" t="b">
+      <c r="O2" s="4" t="b">
         <f>TRUE()</f>
         <v>1</v>
       </c>
-      <c r="P2" s="5" t="b">
+      <c r="P2" s="4" t="b">
         <f>FALSE()</f>
         <v>0</v>
       </c>
-      <c r="Q2" s="6" t="s">
+      <c r="Q2" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="R2" s="6" t="s">
+      <c r="R2" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="S2" s="6" t="s">
+      <c r="S2" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="T2" s="5" t="b">
+      <c r="T2" s="4" t="b">
         <f>TRUE()</f>
         <v>1</v>
       </c>
-      <c r="U2" s="6" t="s">
+      <c r="U2" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="V2" s="8" t="s">
+      <c r="V2" s="7" t="s">
         <v>36</v>
       </c>
       <c r="W2" t="s">
         <v>42</v>
       </c>
-      <c r="X2" s="3" t="s">
+      <c r="X2" s="5" t="s">
         <v>31</v>
       </c>
       <c r="Y2">
@@ -1282,14 +1274,14 @@
         <v>37288</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
       <c r="D5" s="2"/>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="K11" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="22" type="noConversion"/>
+  <phoneticPr fontId="21" type="noConversion"/>
   <conditionalFormatting sqref="C3:C1048576">
     <cfRule type="expression" dxfId="4" priority="12">
       <formula>NOT(AND(ISNUMBER(VALUE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($C3,"-",""),"(",""),")","")," ",""),"+",""))),LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($C3,"-",""),"(",""),")","")," ",""),"+",""))=10))</formula>
@@ -1340,7 +1332,6 @@
       <formula1>0</formula1>
       <formula2>1111</formula2>
     </dataValidation>
-    <dataValidation operator="equal" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Preffered Location" prompt="You can select multiple options from the following_x000a_LOCAL_x000a_OTR_x000a_REGIONAL" sqref="X1:X1048576" xr:uid="{00000000-0002-0000-0000-000009000000}"/>
     <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Input" error="The entered value does not meet the criteria for a valid phone number." promptTitle="Job ID Input" prompt="Please enter a valid job ID. " sqref="Y1:Y1048576" xr:uid="{00000000-0002-0000-0000-000010000000}">
       <formula1>0</formula1>
       <formula2>1111</formula2>
@@ -1367,15 +1358,12 @@
     <dataValidation type="custom" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Input" error="Invalid input. Text only allowed." promptTitle="Text Input Only" prompt="Please enter text only." sqref="A1:B1048576" xr:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>OR(AND(ISTEXT(A1),LEN(A1)&gt;0),AND(ISTEXT(B1),LEN(B1)&gt;0))</formula1>
     </dataValidation>
-    <dataValidation type="list" operator="equal" showInputMessage="1" showErrorMessage="1" errorTitle="Transmission Type" error="Please add proper value" promptTitle="The accepted transmission types are as follows" prompt="MANUAL_x000a_AUTOMATIC_x000a__x000a_Note : Input is Case Sensitive." sqref="Q1:Q1048576" xr:uid="{F1837357-7950-4B3E-A028-6648D396773F}">
-      <formula1>"MANUAL,AUTOMATIC"</formula1>
-    </dataValidation>
     <dataValidation type="list" operator="equal" showInputMessage="1" showErrorMessage="1" errorTitle="Highest Degree" error="Please put proper value" promptTitle="The valid highest degress values are the following:" prompt="HIGH_SCHOOL_x000a_ASSOCIATE_x000a_BACHELOR_x000a_MASTER_x000a_DOCTORAL_x000a__x000a_Note : Input is Case Sensitive." sqref="S1:S1048576" xr:uid="{307E0ED1-EF36-40E6-A6FC-6BC469296874}">
       <formula1>"HIGH_SCHOOL,ASSOCIATE,BACHELOR,MASTER,DOCTORAL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Select Endorsement" prompt="Please select endorsement from the following;_x000a_HAZMAT_x000a_TANKERS_x000a_DOUBLES_TRIPLES_x000a_SCHOOL_BUS_x000a_TWIC_x000a__x000a_Note : Input is Case Sensitive." sqref="R1:R1048576" xr:uid="{D3925612-47AF-45A8-8921-F9A5CAF2C550}">
-      <formula1>"HAZMAT,TANKERS,DOUBLES_TRIPLES,SCHOOL_BUS,TWIC"</formula1>
-    </dataValidation>
+    <dataValidation operator="equal" showInputMessage="1" showErrorMessage="1" errorTitle="Transmission Type" error="Please add proper value" promptTitle="The accepted transmission types are as follows" prompt="MANUAL_x000a_AUTOMATIC_x000a__x000a_Note : Input is Case Sensitive." sqref="Q1:Q1048576" xr:uid="{DC1D4751-F46A-4082-B72B-8B1B1CB8D154}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Endorsements/TWIC" prompt="Please add endorsements and qualifications you have:_x000a_HAZMAT_x000a_TANKERS_x000a_DOUBLES_TRIPLES_x000a_SCHOOL_BUS_x000a_TWIC_x000a__x000a_Note : Input is Case Sensitive." sqref="R1:R1048576" xr:uid="{7222FCD8-EB7B-414E-9784-A9CAC54A64C0}"/>
+    <dataValidation operator="equal" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Preferred Location" prompt="You can add multiple options from the following;_x000a_LOCAL_x000a_OTR_x000a_REGIONAL" sqref="X1:X1048576" xr:uid="{9C05345C-61C0-49A7-A711-C19FD51916FC}"/>
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="D2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
